--- a/Assets/Resources/Data/Excel/PlayerData.xlsx
+++ b/Assets/Resources/Data/Excel/PlayerData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90893411-EAF7-4D15-B5B8-2FEFC3F68890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD199E2-0CB6-48A2-9CE5-457AD10219B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{6664469C-7E4F-4B40-B07F-12AD1063489B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{6664469C-7E4F-4B40-B07F-12AD1063489B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,18 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/UI/Battle/NameIcon/Player/K_Battle_Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Battle/NameIcon/Player/Chloe_Battle_Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/UI/Battle/NameIcon/Player/Svana_Battle_Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>resBleed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -158,6 +146,18 @@
   </si>
   <si>
     <t>resMove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Battle/NameIcon/Player/K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Battle/NameIcon/Player/Chloe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Battle/NameIcon/Player/Svana</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,25 +572,25 @@
         <v>21</v>
       </c>
       <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" t="s">
         <v>29</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>31</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>32</v>
-      </c>
-      <c r="S1" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1" t="s">
-        <v>35</v>
       </c>
       <c r="V1" t="s">
         <v>3</v>
@@ -634,7 +634,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>65</v>
@@ -649,7 +649,7 @@
         <v>15</v>
       </c>
       <c r="J2">
-        <v>90</v>
+        <v>0.9</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>50</v>
@@ -741,7 +741,7 @@
         <v>18</v>
       </c>
       <c r="J3">
-        <v>85</v>
+        <v>0.85</v>
       </c>
       <c r="K3">
         <v>30</v>
@@ -818,7 +818,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>46</v>
@@ -833,7 +833,7 @@
         <v>18</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>0.85</v>
       </c>
       <c r="K4">
         <v>30</v>
